--- a/selenium-tests/test_results.xlsx
+++ b/selenium-tests/test_results.xlsx
@@ -417,7 +417,7 @@
         <v>Timestamp</v>
       </c>
       <c r="B2" t="str">
-        <v>24/7/2026, 2:51:33 pm</v>
+        <v>25/7/2026, 12:44:39 am</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         <v>Total Execution Duration</v>
       </c>
       <c r="B10" t="str">
-        <v>4.75 seconds</v>
+        <v>4.80 seconds</v>
       </c>
     </row>
   </sheetData>
@@ -558,7 +558,7 @@
         <v>PASS</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I2" t="str">
         <v>Low</v>
@@ -587,7 +587,7 @@
         <v>PASS</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I3" t="str">
         <v>Medium</v>
@@ -616,7 +616,7 @@
         <v>PASS</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I4" t="str">
         <v>High</v>
@@ -645,7 +645,7 @@
         <v>PASS</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="str">
         <v>Critical</v>
@@ -674,7 +674,7 @@
         <v>PASS</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I6" t="str">
         <v>Low</v>
@@ -703,7 +703,7 @@
         <v>PASS</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I7" t="str">
         <v>High</v>
@@ -732,7 +732,7 @@
         <v>PASS</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I8" t="str">
         <v>Low</v>
@@ -761,7 +761,7 @@
         <v>PASS</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I9" t="str">
         <v>Critical</v>
@@ -790,7 +790,7 @@
         <v>PASS</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I10" t="str">
         <v>High</v>
@@ -819,7 +819,7 @@
         <v>PASS</v>
       </c>
       <c r="H11">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I11" t="str">
         <v>Medium</v>
@@ -848,7 +848,7 @@
         <v>PASS</v>
       </c>
       <c r="H12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I12" t="str">
         <v>Low</v>
@@ -906,7 +906,7 @@
         <v>PASS</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I14" t="str">
         <v>High</v>
@@ -935,7 +935,7 @@
         <v>PASS</v>
       </c>
       <c r="H15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I15" t="str">
         <v>Critical</v>
@@ -964,7 +964,7 @@
         <v>PASS</v>
       </c>
       <c r="H16">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I16" t="str">
         <v>Low</v>
@@ -993,7 +993,7 @@
         <v>PASS</v>
       </c>
       <c r="H17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I17" t="str">
         <v>High</v>
@@ -1022,7 +1022,7 @@
         <v>PASS</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I18" t="str">
         <v>Low</v>
@@ -1051,7 +1051,7 @@
         <v>PASS</v>
       </c>
       <c r="H19">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I19" t="str">
         <v>Critical</v>
@@ -1080,7 +1080,7 @@
         <v>PASS</v>
       </c>
       <c r="H20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" t="str">
         <v>High</v>
@@ -1109,7 +1109,7 @@
         <v>PASS</v>
       </c>
       <c r="H21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" t="str">
         <v>Medium</v>
@@ -1138,7 +1138,7 @@
         <v>PASS</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I22" t="str">
         <v>Low</v>
@@ -1167,7 +1167,7 @@
         <v>PASS</v>
       </c>
       <c r="H23">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I23" t="str">
         <v>Medium</v>
@@ -1196,7 +1196,7 @@
         <v>PASS</v>
       </c>
       <c r="H24">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I24" t="str">
         <v>High</v>
@@ -1225,7 +1225,7 @@
         <v>PASS</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I25" t="str">
         <v>Critical</v>
@@ -1254,7 +1254,7 @@
         <v>PASS</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I26" t="str">
         <v>Low</v>
@@ -1283,7 +1283,7 @@
         <v>PASS</v>
       </c>
       <c r="H27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="str">
         <v>High</v>
@@ -1312,7 +1312,7 @@
         <v>PASS</v>
       </c>
       <c r="H28">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28" t="str">
         <v>Low</v>
@@ -1341,7 +1341,7 @@
         <v>PASS</v>
       </c>
       <c r="H29">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I29" t="str">
         <v>Critical</v>
@@ -1370,7 +1370,7 @@
         <v>PASS</v>
       </c>
       <c r="H30">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I30" t="str">
         <v>High</v>
@@ -1399,7 +1399,7 @@
         <v>PASS</v>
       </c>
       <c r="H31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I31" t="str">
         <v>Medium</v>
@@ -1428,7 +1428,7 @@
         <v>PASS</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I32" t="str">
         <v>Low</v>
@@ -1457,7 +1457,7 @@
         <v>PASS</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I33" t="str">
         <v>Medium</v>
@@ -1486,7 +1486,7 @@
         <v>PASS</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I34" t="str">
         <v>High</v>
@@ -1515,7 +1515,7 @@
         <v>PASS</v>
       </c>
       <c r="H35">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I35" t="str">
         <v>Critical</v>
@@ -1544,7 +1544,7 @@
         <v>PASS</v>
       </c>
       <c r="H36">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I36" t="str">
         <v>Low</v>
@@ -1573,7 +1573,7 @@
         <v>PASS</v>
       </c>
       <c r="H37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I37" t="str">
         <v>High</v>
@@ -1602,7 +1602,7 @@
         <v>PASS</v>
       </c>
       <c r="H38">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I38" t="str">
         <v>Low</v>
@@ -1631,7 +1631,7 @@
         <v>PASS</v>
       </c>
       <c r="H39">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I39" t="str">
         <v>Critical</v>
@@ -1660,7 +1660,7 @@
         <v>PASS</v>
       </c>
       <c r="H40">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I40" t="str">
         <v>High</v>
@@ -1689,7 +1689,7 @@
         <v>PASS</v>
       </c>
       <c r="H41">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I41" t="str">
         <v>Medium</v>
@@ -1718,7 +1718,7 @@
         <v>PASS</v>
       </c>
       <c r="H42">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I42" t="str">
         <v>Low</v>
@@ -1776,7 +1776,7 @@
         <v>PASS</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" t="str">
         <v>High</v>
@@ -1805,7 +1805,7 @@
         <v>PASS</v>
       </c>
       <c r="H45">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I45" t="str">
         <v>Critical</v>
@@ -1834,7 +1834,7 @@
         <v>PASS</v>
       </c>
       <c r="H46">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I46" t="str">
         <v>Low</v>
@@ -1863,7 +1863,7 @@
         <v>PASS</v>
       </c>
       <c r="H47">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" t="str">
         <v>High</v>
@@ -1892,7 +1892,7 @@
         <v>PASS</v>
       </c>
       <c r="H48">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I48" t="str">
         <v>Low</v>
@@ -1921,7 +1921,7 @@
         <v>PASS</v>
       </c>
       <c r="H49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <v>Critical</v>
@@ -1950,7 +1950,7 @@
         <v>PASS</v>
       </c>
       <c r="H50">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="str">
         <v>High</v>
@@ -1979,7 +1979,7 @@
         <v>PASS</v>
       </c>
       <c r="H51">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I51" t="str">
         <v>Medium</v>
@@ -2037,7 +2037,7 @@
         <v>PASS</v>
       </c>
       <c r="H53">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I53" t="str">
         <v>Medium</v>
@@ -2066,7 +2066,7 @@
         <v>PASS</v>
       </c>
       <c r="H54">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I54" t="str">
         <v>High</v>
@@ -2095,7 +2095,7 @@
         <v>PASS</v>
       </c>
       <c r="H55">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I55" t="str">
         <v>Critical</v>
@@ -2124,7 +2124,7 @@
         <v>PASS</v>
       </c>
       <c r="H56">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I56" t="str">
         <v>Low</v>
@@ -2153,7 +2153,7 @@
         <v>PASS</v>
       </c>
       <c r="H57">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I57" t="str">
         <v>High</v>
@@ -2182,7 +2182,7 @@
         <v>PASS</v>
       </c>
       <c r="H58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I58" t="str">
         <v>Low</v>
@@ -2211,7 +2211,7 @@
         <v>PASS</v>
       </c>
       <c r="H59">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I59" t="str">
         <v>Critical</v>
@@ -2240,7 +2240,7 @@
         <v>PASS</v>
       </c>
       <c r="H60">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I60" t="str">
         <v>High</v>
@@ -2269,7 +2269,7 @@
         <v>PASS</v>
       </c>
       <c r="H61">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I61" t="str">
         <v>Medium</v>
@@ -2298,7 +2298,7 @@
         <v>PASS</v>
       </c>
       <c r="H62">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I62" t="str">
         <v>Low</v>
@@ -2327,7 +2327,7 @@
         <v>PASS</v>
       </c>
       <c r="H63">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I63" t="str">
         <v>Medium</v>
@@ -2385,7 +2385,7 @@
         <v>PASS</v>
       </c>
       <c r="H65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I65" t="str">
         <v>Critical</v>
@@ -2414,7 +2414,7 @@
         <v>PASS</v>
       </c>
       <c r="H66">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I66" t="str">
         <v>Low</v>
@@ -2443,7 +2443,7 @@
         <v>PASS</v>
       </c>
       <c r="H67">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I67" t="str">
         <v>High</v>
@@ -2472,7 +2472,7 @@
         <v>PASS</v>
       </c>
       <c r="H68">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I68" t="str">
         <v>Low</v>
@@ -2501,7 +2501,7 @@
         <v>PASS</v>
       </c>
       <c r="H69">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v>Critical</v>
@@ -2530,7 +2530,7 @@
         <v>PASS</v>
       </c>
       <c r="H70">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" t="str">
         <v>High</v>
@@ -2559,7 +2559,7 @@
         <v>PASS</v>
       </c>
       <c r="H71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I71" t="str">
         <v>Medium</v>
@@ -2588,7 +2588,7 @@
         <v>PASS</v>
       </c>
       <c r="H72">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I72" t="str">
         <v>Low</v>
@@ -2617,7 +2617,7 @@
         <v>PASS</v>
       </c>
       <c r="H73">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I73" t="str">
         <v>Medium</v>
@@ -2646,7 +2646,7 @@
         <v>PASS</v>
       </c>
       <c r="H74">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
         <v>High</v>
@@ -2704,7 +2704,7 @@
         <v>PASS</v>
       </c>
       <c r="H76">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I76" t="str">
         <v>Low</v>
@@ -2733,7 +2733,7 @@
         <v>PASS</v>
       </c>
       <c r="H77">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I77" t="str">
         <v>High</v>
@@ -2762,7 +2762,7 @@
         <v>PASS</v>
       </c>
       <c r="H78">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I78" t="str">
         <v>Low</v>
@@ -2791,7 +2791,7 @@
         <v>PASS</v>
       </c>
       <c r="H79">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I79" t="str">
         <v>Critical</v>
@@ -2820,7 +2820,7 @@
         <v>PASS</v>
       </c>
       <c r="H80">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I80" t="str">
         <v>High</v>
@@ -2849,7 +2849,7 @@
         <v>PASS</v>
       </c>
       <c r="H81">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I81" t="str">
         <v>Medium</v>
@@ -2878,7 +2878,7 @@
         <v>PASS</v>
       </c>
       <c r="H82">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I82" t="str">
         <v>Low</v>
@@ -2907,7 +2907,7 @@
         <v>PASS</v>
       </c>
       <c r="H83">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I83" t="str">
         <v>Medium</v>
@@ -2936,7 +2936,7 @@
         <v>PASS</v>
       </c>
       <c r="H84">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I84" t="str">
         <v>High</v>
@@ -2965,7 +2965,7 @@
         <v>PASS</v>
       </c>
       <c r="H85">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I85" t="str">
         <v>Critical</v>
@@ -2994,7 +2994,7 @@
         <v>PASS</v>
       </c>
       <c r="H86">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I86" t="str">
         <v>Low</v>
@@ -3023,7 +3023,7 @@
         <v>PASS</v>
       </c>
       <c r="H87">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I87" t="str">
         <v>High</v>
@@ -3052,7 +3052,7 @@
         <v>PASS</v>
       </c>
       <c r="H88">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I88" t="str">
         <v>Low</v>
@@ -3081,7 +3081,7 @@
         <v>PASS</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I89" t="str">
         <v>Critical</v>
@@ -3110,7 +3110,7 @@
         <v>PASS</v>
       </c>
       <c r="H90">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I90" t="str">
         <v>High</v>
@@ -3139,7 +3139,7 @@
         <v>PASS</v>
       </c>
       <c r="H91">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I91" t="str">
         <v>Medium</v>
@@ -3168,7 +3168,7 @@
         <v>PASS</v>
       </c>
       <c r="H92">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I92" t="str">
         <v>Low</v>
@@ -3197,7 +3197,7 @@
         <v>PASS</v>
       </c>
       <c r="H93">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I93" t="str">
         <v>Medium</v>
@@ -3226,7 +3226,7 @@
         <v>PASS</v>
       </c>
       <c r="H94">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I94" t="str">
         <v>High</v>
@@ -3255,7 +3255,7 @@
         <v>PASS</v>
       </c>
       <c r="H95">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I95" t="str">
         <v>Critical</v>
@@ -3284,7 +3284,7 @@
         <v>PASS</v>
       </c>
       <c r="H96">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I96" t="str">
         <v>Low</v>
@@ -3313,7 +3313,7 @@
         <v>PASS</v>
       </c>
       <c r="H97">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I97" t="str">
         <v>High</v>
@@ -3342,7 +3342,7 @@
         <v>PASS</v>
       </c>
       <c r="H98">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I98" t="str">
         <v>Low</v>
@@ -3371,7 +3371,7 @@
         <v>PASS</v>
       </c>
       <c r="H99">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I99" t="str">
         <v>Critical</v>
@@ -3400,7 +3400,7 @@
         <v>PASS</v>
       </c>
       <c r="H100">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I100" t="str">
         <v>High</v>
@@ -3429,7 +3429,7 @@
         <v>PASS</v>
       </c>
       <c r="H101">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I101" t="str">
         <v>Medium</v>
@@ -3458,7 +3458,7 @@
         <v>PASS</v>
       </c>
       <c r="H102">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I102" t="str">
         <v>Low</v>
@@ -3487,7 +3487,7 @@
         <v>PASS</v>
       </c>
       <c r="H103">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I103" t="str">
         <v>Medium</v>
@@ -3516,7 +3516,7 @@
         <v>PASS</v>
       </c>
       <c r="H104">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I104" t="str">
         <v>High</v>
@@ -3545,7 +3545,7 @@
         <v>PASS</v>
       </c>
       <c r="H105">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I105" t="str">
         <v>Critical</v>
@@ -3574,7 +3574,7 @@
         <v>PASS</v>
       </c>
       <c r="H106">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I106" t="str">
         <v>Low</v>
@@ -3603,7 +3603,7 @@
         <v>PASS</v>
       </c>
       <c r="H107">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I107" t="str">
         <v>High</v>
@@ -3632,7 +3632,7 @@
         <v>PASS</v>
       </c>
       <c r="H108">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I108" t="str">
         <v>Low</v>
@@ -3661,7 +3661,7 @@
         <v>PASS</v>
       </c>
       <c r="H109">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I109" t="str">
         <v>Critical</v>
@@ -3690,7 +3690,7 @@
         <v>PASS</v>
       </c>
       <c r="H110">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I110" t="str">
         <v>High</v>
@@ -3719,7 +3719,7 @@
         <v>PASS</v>
       </c>
       <c r="H111">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I111" t="str">
         <v>Medium</v>
@@ -3748,7 +3748,7 @@
         <v>PASS</v>
       </c>
       <c r="H112">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I112" t="str">
         <v>Low</v>
@@ -3777,7 +3777,7 @@
         <v>PASS</v>
       </c>
       <c r="H113">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I113" t="str">
         <v>Medium</v>
@@ -3806,7 +3806,7 @@
         <v>PASS</v>
       </c>
       <c r="H114">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I114" t="str">
         <v>High</v>
@@ -3835,7 +3835,7 @@
         <v>PASS</v>
       </c>
       <c r="H115">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I115" t="str">
         <v>Critical</v>
@@ -3864,7 +3864,7 @@
         <v>PASS</v>
       </c>
       <c r="H116">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I116" t="str">
         <v>Low</v>
@@ -3893,7 +3893,7 @@
         <v>PASS</v>
       </c>
       <c r="H117">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I117" t="str">
         <v>High</v>
@@ -3922,7 +3922,7 @@
         <v>PASS</v>
       </c>
       <c r="H118">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I118" t="str">
         <v>Low</v>
@@ -3951,7 +3951,7 @@
         <v>PASS</v>
       </c>
       <c r="H119">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I119" t="str">
         <v>Critical</v>
@@ -3980,7 +3980,7 @@
         <v>PASS</v>
       </c>
       <c r="H120">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I120" t="str">
         <v>High</v>
@@ -4009,7 +4009,7 @@
         <v>PASS</v>
       </c>
       <c r="H121">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I121" t="str">
         <v>Medium</v>
@@ -4038,7 +4038,7 @@
         <v>PASS</v>
       </c>
       <c r="H122">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I122" t="str">
         <v>Low</v>
@@ -4067,7 +4067,7 @@
         <v>PASS</v>
       </c>
       <c r="H123">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I123" t="str">
         <v>Medium</v>
@@ -4096,7 +4096,7 @@
         <v>PASS</v>
       </c>
       <c r="H124">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I124" t="str">
         <v>High</v>
@@ -4125,7 +4125,7 @@
         <v>PASS</v>
       </c>
       <c r="H125">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I125" t="str">
         <v>Critical</v>
@@ -4154,7 +4154,7 @@
         <v>PASS</v>
       </c>
       <c r="H126">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I126" t="str">
         <v>Low</v>
@@ -4183,7 +4183,7 @@
         <v>PASS</v>
       </c>
       <c r="H127">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I127" t="str">
         <v>High</v>
@@ -4241,7 +4241,7 @@
         <v>PASS</v>
       </c>
       <c r="H129">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I129" t="str">
         <v>Critical</v>
@@ -4270,7 +4270,7 @@
         <v>PASS</v>
       </c>
       <c r="H130">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I130" t="str">
         <v>High</v>
@@ -4299,7 +4299,7 @@
         <v>PASS</v>
       </c>
       <c r="H131">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="I131" t="str">
         <v>Medium</v>
@@ -4328,7 +4328,7 @@
         <v>PASS</v>
       </c>
       <c r="H132">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I132" t="str">
         <v>Low</v>
@@ -4357,7 +4357,7 @@
         <v>PASS</v>
       </c>
       <c r="H133">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I133" t="str">
         <v>Medium</v>
@@ -4386,7 +4386,7 @@
         <v>PASS</v>
       </c>
       <c r="H134">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I134" t="str">
         <v>High</v>
@@ -4415,7 +4415,7 @@
         <v>PASS</v>
       </c>
       <c r="H135">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I135" t="str">
         <v>Critical</v>
@@ -4444,7 +4444,7 @@
         <v>PASS</v>
       </c>
       <c r="H136">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I136" t="str">
         <v>Low</v>
@@ -4473,7 +4473,7 @@
         <v>PASS</v>
       </c>
       <c r="H137">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I137" t="str">
         <v>High</v>
@@ -4502,7 +4502,7 @@
         <v>PASS</v>
       </c>
       <c r="H138">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I138" t="str">
         <v>Low</v>
@@ -4531,7 +4531,7 @@
         <v>PASS</v>
       </c>
       <c r="H139">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I139" t="str">
         <v>Critical</v>
@@ -4560,7 +4560,7 @@
         <v>PASS</v>
       </c>
       <c r="H140">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I140" t="str">
         <v>High</v>
@@ -4589,7 +4589,7 @@
         <v>PASS</v>
       </c>
       <c r="H141">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I141" t="str">
         <v>Medium</v>
@@ -4618,7 +4618,7 @@
         <v>PASS</v>
       </c>
       <c r="H142">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I142" t="str">
         <v>Low</v>
@@ -4647,7 +4647,7 @@
         <v>PASS</v>
       </c>
       <c r="H143">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I143" t="str">
         <v>Medium</v>
@@ -4676,7 +4676,7 @@
         <v>PASS</v>
       </c>
       <c r="H144">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I144" t="str">
         <v>High</v>
@@ -4705,7 +4705,7 @@
         <v>PASS</v>
       </c>
       <c r="H145">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I145" t="str">
         <v>Critical</v>
@@ -4734,7 +4734,7 @@
         <v>PASS</v>
       </c>
       <c r="H146">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I146" t="str">
         <v>Low</v>
@@ -4763,7 +4763,7 @@
         <v>PASS</v>
       </c>
       <c r="H147">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I147" t="str">
         <v>High</v>
@@ -4792,7 +4792,7 @@
         <v>PASS</v>
       </c>
       <c r="H148">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I148" t="str">
         <v>Low</v>
@@ -4821,7 +4821,7 @@
         <v>PASS</v>
       </c>
       <c r="H149">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I149" t="str">
         <v>Critical</v>
@@ -4850,7 +4850,7 @@
         <v>PASS</v>
       </c>
       <c r="H150">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I150" t="str">
         <v>High</v>
@@ -4879,7 +4879,7 @@
         <v>PASS</v>
       </c>
       <c r="H151">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I151" t="str">
         <v>Medium</v>
@@ -4908,7 +4908,7 @@
         <v>PASS</v>
       </c>
       <c r="H152">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I152" t="str">
         <v>Low</v>
@@ -4937,7 +4937,7 @@
         <v>PASS</v>
       </c>
       <c r="H153">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I153" t="str">
         <v>Medium</v>
@@ -4966,7 +4966,7 @@
         <v>PASS</v>
       </c>
       <c r="H154">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I154" t="str">
         <v>High</v>
@@ -4995,7 +4995,7 @@
         <v>PASS</v>
       </c>
       <c r="H155">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I155" t="str">
         <v>Critical</v>
@@ -5024,7 +5024,7 @@
         <v>PASS</v>
       </c>
       <c r="H156">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I156" t="str">
         <v>Low</v>
@@ -5053,7 +5053,7 @@
         <v>PASS</v>
       </c>
       <c r="H157">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I157" t="str">
         <v>High</v>
@@ -5082,7 +5082,7 @@
         <v>PASS</v>
       </c>
       <c r="H158">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I158" t="str">
         <v>Low</v>
@@ -5111,7 +5111,7 @@
         <v>PASS</v>
       </c>
       <c r="H159">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I159" t="str">
         <v>Critical</v>
@@ -5140,7 +5140,7 @@
         <v>PASS</v>
       </c>
       <c r="H160">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I160" t="str">
         <v>High</v>
@@ -5169,7 +5169,7 @@
         <v>PASS</v>
       </c>
       <c r="H161">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I161" t="str">
         <v>Medium</v>
@@ -5198,7 +5198,7 @@
         <v>PASS</v>
       </c>
       <c r="H162">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I162" t="str">
         <v>Low</v>
@@ -5227,7 +5227,7 @@
         <v>PASS</v>
       </c>
       <c r="H163">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I163" t="str">
         <v>Medium</v>
@@ -5256,7 +5256,7 @@
         <v>PASS</v>
       </c>
       <c r="H164">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I164" t="str">
         <v>High</v>
@@ -5285,7 +5285,7 @@
         <v>PASS</v>
       </c>
       <c r="H165">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I165" t="str">
         <v>Critical</v>
@@ -5314,7 +5314,7 @@
         <v>PASS</v>
       </c>
       <c r="H166">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I166" t="str">
         <v>Low</v>
@@ -5343,7 +5343,7 @@
         <v>PASS</v>
       </c>
       <c r="H167">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I167" t="str">
         <v>High</v>
@@ -5372,7 +5372,7 @@
         <v>PASS</v>
       </c>
       <c r="H168">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I168" t="str">
         <v>Low</v>
@@ -5401,7 +5401,7 @@
         <v>PASS</v>
       </c>
       <c r="H169">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I169" t="str">
         <v>Critical</v>
@@ -5430,7 +5430,7 @@
         <v>PASS</v>
       </c>
       <c r="H170">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I170" t="str">
         <v>High</v>
@@ -5459,7 +5459,7 @@
         <v>PASS</v>
       </c>
       <c r="H171">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I171" t="str">
         <v>Medium</v>
@@ -5488,7 +5488,7 @@
         <v>PASS</v>
       </c>
       <c r="H172">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I172" t="str">
         <v>Low</v>
@@ -5517,7 +5517,7 @@
         <v>PASS</v>
       </c>
       <c r="H173">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I173" t="str">
         <v>Medium</v>
@@ -5546,7 +5546,7 @@
         <v>PASS</v>
       </c>
       <c r="H174">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I174" t="str">
         <v>High</v>
@@ -5575,7 +5575,7 @@
         <v>PASS</v>
       </c>
       <c r="H175">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I175" t="str">
         <v>Critical</v>
@@ -5604,7 +5604,7 @@
         <v>PASS</v>
       </c>
       <c r="H176">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I176" t="str">
         <v>Low</v>
@@ -5633,7 +5633,7 @@
         <v>PASS</v>
       </c>
       <c r="H177">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I177" t="str">
         <v>High</v>
@@ -5662,7 +5662,7 @@
         <v>PASS</v>
       </c>
       <c r="H178">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I178" t="str">
         <v>Low</v>
@@ -5691,7 +5691,7 @@
         <v>PASS</v>
       </c>
       <c r="H179">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I179" t="str">
         <v>Critical</v>
@@ -5720,7 +5720,7 @@
         <v>PASS</v>
       </c>
       <c r="H180">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I180" t="str">
         <v>High</v>
@@ -5778,7 +5778,7 @@
         <v>PASS</v>
       </c>
       <c r="H182">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I182" t="str">
         <v>Low</v>
@@ -5807,7 +5807,7 @@
         <v>PASS</v>
       </c>
       <c r="H183">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I183" t="str">
         <v>Medium</v>
@@ -5836,7 +5836,7 @@
         <v>PASS</v>
       </c>
       <c r="H184">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I184" t="str">
         <v>High</v>
@@ -5865,7 +5865,7 @@
         <v>PASS</v>
       </c>
       <c r="H185">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I185" t="str">
         <v>Critical</v>
@@ -5894,7 +5894,7 @@
         <v>PASS</v>
       </c>
       <c r="H186">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I186" t="str">
         <v>Low</v>
@@ -5952,7 +5952,7 @@
         <v>PASS</v>
       </c>
       <c r="H188">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I188" t="str">
         <v>Low</v>
@@ -5981,7 +5981,7 @@
         <v>PASS</v>
       </c>
       <c r="H189">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I189" t="str">
         <v>Critical</v>
@@ -6010,7 +6010,7 @@
         <v>PASS</v>
       </c>
       <c r="H190">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I190" t="str">
         <v>High</v>
@@ -6039,7 +6039,7 @@
         <v>PASS</v>
       </c>
       <c r="H191">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I191" t="str">
         <v>Medium</v>
@@ -6068,7 +6068,7 @@
         <v>PASS</v>
       </c>
       <c r="H192">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I192" t="str">
         <v>Low</v>
@@ -6097,7 +6097,7 @@
         <v>PASS</v>
       </c>
       <c r="H193">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I193" t="str">
         <v>Medium</v>
@@ -6126,7 +6126,7 @@
         <v>PASS</v>
       </c>
       <c r="H194">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I194" t="str">
         <v>High</v>
@@ -6155,7 +6155,7 @@
         <v>PASS</v>
       </c>
       <c r="H195">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I195" t="str">
         <v>Critical</v>
@@ -6184,7 +6184,7 @@
         <v>PASS</v>
       </c>
       <c r="H196">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I196" t="str">
         <v>Low</v>
@@ -6213,7 +6213,7 @@
         <v>PASS</v>
       </c>
       <c r="H197">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I197" t="str">
         <v>High</v>
@@ -6242,7 +6242,7 @@
         <v>PASS</v>
       </c>
       <c r="H198">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I198" t="str">
         <v>Low</v>
@@ -6271,7 +6271,7 @@
         <v>PASS</v>
       </c>
       <c r="H199">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I199" t="str">
         <v>Critical</v>
@@ -6300,7 +6300,7 @@
         <v>PASS</v>
       </c>
       <c r="H200">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I200" t="str">
         <v>High</v>
@@ -6329,7 +6329,7 @@
         <v>PASS</v>
       </c>
       <c r="H201">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I201" t="str">
         <v>Medium</v>
@@ -6358,7 +6358,7 @@
         <v>PASS</v>
       </c>
       <c r="H202">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I202" t="str">
         <v>Low</v>
@@ -6387,7 +6387,7 @@
         <v>PASS</v>
       </c>
       <c r="H203">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I203" t="str">
         <v>Medium</v>
@@ -6416,7 +6416,7 @@
         <v>PASS</v>
       </c>
       <c r="H204">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I204" t="str">
         <v>High</v>
@@ -6445,7 +6445,7 @@
         <v>PASS</v>
       </c>
       <c r="H205">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I205" t="str">
         <v>Critical</v>
@@ -6474,7 +6474,7 @@
         <v>PASS</v>
       </c>
       <c r="H206">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I206" t="str">
         <v>Low</v>
@@ -6561,7 +6561,7 @@
         <v>PASS</v>
       </c>
       <c r="H209">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I209" t="str">
         <v>Critical</v>
@@ -6590,7 +6590,7 @@
         <v>PASS</v>
       </c>
       <c r="H210">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I210" t="str">
         <v>High</v>
@@ -6619,7 +6619,7 @@
         <v>PASS</v>
       </c>
       <c r="H211">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I211" t="str">
         <v>Medium</v>
@@ -6648,7 +6648,7 @@
         <v>PASS</v>
       </c>
       <c r="H212">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I212" t="str">
         <v>Low</v>
@@ -6677,7 +6677,7 @@
         <v>PASS</v>
       </c>
       <c r="H213">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I213" t="str">
         <v>Medium</v>
@@ -6706,7 +6706,7 @@
         <v>PASS</v>
       </c>
       <c r="H214">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I214" t="str">
         <v>High</v>
@@ -6735,7 +6735,7 @@
         <v>PASS</v>
       </c>
       <c r="H215">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I215" t="str">
         <v>Critical</v>
@@ -6764,7 +6764,7 @@
         <v>PASS</v>
       </c>
       <c r="H216">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I216" t="str">
         <v>Low</v>
@@ -6793,7 +6793,7 @@
         <v>PASS</v>
       </c>
       <c r="H217">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I217" t="str">
         <v>High</v>
@@ -6822,7 +6822,7 @@
         <v>PASS</v>
       </c>
       <c r="H218">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I218" t="str">
         <v>Low</v>
@@ -6851,7 +6851,7 @@
         <v>PASS</v>
       </c>
       <c r="H219">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I219" t="str">
         <v>Critical</v>
@@ -6880,7 +6880,7 @@
         <v>PASS</v>
       </c>
       <c r="H220">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I220" t="str">
         <v>High</v>
@@ -6909,7 +6909,7 @@
         <v>PASS</v>
       </c>
       <c r="H221">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I221" t="str">
         <v>Medium</v>
@@ -6938,7 +6938,7 @@
         <v>PASS</v>
       </c>
       <c r="H222">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I222" t="str">
         <v>Low</v>
@@ -6967,7 +6967,7 @@
         <v>PASS</v>
       </c>
       <c r="H223">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I223" t="str">
         <v>Medium</v>
@@ -6996,7 +6996,7 @@
         <v>PASS</v>
       </c>
       <c r="H224">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I224" t="str">
         <v>High</v>
@@ -7025,7 +7025,7 @@
         <v>PASS</v>
       </c>
       <c r="H225">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I225" t="str">
         <v>Critical</v>
@@ -7054,7 +7054,7 @@
         <v>PASS</v>
       </c>
       <c r="H226">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I226" t="str">
         <v>Low</v>
@@ -7083,7 +7083,7 @@
         <v>PASS</v>
       </c>
       <c r="H227">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I227" t="str">
         <v>High</v>
@@ -7112,7 +7112,7 @@
         <v>PASS</v>
       </c>
       <c r="H228">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I228" t="str">
         <v>Low</v>
@@ -7141,7 +7141,7 @@
         <v>PASS</v>
       </c>
       <c r="H229">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I229" t="str">
         <v>Critical</v>
@@ -7170,7 +7170,7 @@
         <v>PASS</v>
       </c>
       <c r="H230">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I230" t="str">
         <v>High</v>
@@ -7199,7 +7199,7 @@
         <v>PASS</v>
       </c>
       <c r="H231">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I231" t="str">
         <v>Medium</v>
@@ -7228,7 +7228,7 @@
         <v>PASS</v>
       </c>
       <c r="H232">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I232" t="str">
         <v>Low</v>
@@ -7257,7 +7257,7 @@
         <v>PASS</v>
       </c>
       <c r="H233">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I233" t="str">
         <v>Medium</v>
@@ -7286,7 +7286,7 @@
         <v>PASS</v>
       </c>
       <c r="H234">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I234" t="str">
         <v>High</v>
@@ -7315,7 +7315,7 @@
         <v>PASS</v>
       </c>
       <c r="H235">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I235" t="str">
         <v>Critical</v>
@@ -7344,7 +7344,7 @@
         <v>PASS</v>
       </c>
       <c r="H236">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I236" t="str">
         <v>Low</v>
@@ -7373,7 +7373,7 @@
         <v>PASS</v>
       </c>
       <c r="H237">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I237" t="str">
         <v>High</v>
@@ -7402,7 +7402,7 @@
         <v>PASS</v>
       </c>
       <c r="H238">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I238" t="str">
         <v>Low</v>
@@ -7431,7 +7431,7 @@
         <v>PASS</v>
       </c>
       <c r="H239">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I239" t="str">
         <v>Critical</v>
@@ -7460,7 +7460,7 @@
         <v>PASS</v>
       </c>
       <c r="H240">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I240" t="str">
         <v>High</v>
@@ -7489,7 +7489,7 @@
         <v>PASS</v>
       </c>
       <c r="H241">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I241" t="str">
         <v>Medium</v>
@@ -7518,7 +7518,7 @@
         <v>PASS</v>
       </c>
       <c r="H242">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I242" t="str">
         <v>Low</v>
@@ -7547,7 +7547,7 @@
         <v>PASS</v>
       </c>
       <c r="H243">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I243" t="str">
         <v>Medium</v>
@@ -7576,7 +7576,7 @@
         <v>PASS</v>
       </c>
       <c r="H244">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I244" t="str">
         <v>High</v>
@@ -7605,7 +7605,7 @@
         <v>PASS</v>
       </c>
       <c r="H245">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I245" t="str">
         <v>Critical</v>
@@ -7634,7 +7634,7 @@
         <v>PASS</v>
       </c>
       <c r="H246">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I246" t="str">
         <v>Low</v>
@@ -7663,7 +7663,7 @@
         <v>PASS</v>
       </c>
       <c r="H247">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I247" t="str">
         <v>High</v>
@@ -7692,7 +7692,7 @@
         <v>PASS</v>
       </c>
       <c r="H248">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I248" t="str">
         <v>Low</v>
@@ -7721,7 +7721,7 @@
         <v>PASS</v>
       </c>
       <c r="H249">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I249" t="str">
         <v>Critical</v>
@@ -7750,7 +7750,7 @@
         <v>PASS</v>
       </c>
       <c r="H250">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I250" t="str">
         <v>High</v>
@@ -7779,7 +7779,7 @@
         <v>PASS</v>
       </c>
       <c r="H251">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I251" t="str">
         <v>Medium</v>
@@ -7808,7 +7808,7 @@
         <v>PASS</v>
       </c>
       <c r="H252">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I252" t="str">
         <v>Low</v>
@@ -7837,7 +7837,7 @@
         <v>PASS</v>
       </c>
       <c r="H253">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I253" t="str">
         <v>Medium</v>
@@ -7866,7 +7866,7 @@
         <v>PASS</v>
       </c>
       <c r="H254">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I254" t="str">
         <v>High</v>
@@ -7895,7 +7895,7 @@
         <v>PASS</v>
       </c>
       <c r="H255">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I255" t="str">
         <v>Critical</v>
@@ -7924,7 +7924,7 @@
         <v>PASS</v>
       </c>
       <c r="H256">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I256" t="str">
         <v>Low</v>
@@ -7953,7 +7953,7 @@
         <v>PASS</v>
       </c>
       <c r="H257">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I257" t="str">
         <v>High</v>
@@ -7982,7 +7982,7 @@
         <v>PASS</v>
       </c>
       <c r="H258">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I258" t="str">
         <v>Low</v>
@@ -8011,7 +8011,7 @@
         <v>PASS</v>
       </c>
       <c r="H259">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I259" t="str">
         <v>Critical</v>
@@ -8040,7 +8040,7 @@
         <v>PASS</v>
       </c>
       <c r="H260">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I260" t="str">
         <v>High</v>
@@ -8069,7 +8069,7 @@
         <v>PASS</v>
       </c>
       <c r="H261">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I261" t="str">
         <v>Medium</v>
@@ -8098,7 +8098,7 @@
         <v>PASS</v>
       </c>
       <c r="H262">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I262" t="str">
         <v>Low</v>
@@ -8156,7 +8156,7 @@
         <v>PASS</v>
       </c>
       <c r="H264">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I264" t="str">
         <v>High</v>
@@ -8185,7 +8185,7 @@
         <v>PASS</v>
       </c>
       <c r="H265">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I265" t="str">
         <v>Critical</v>
@@ -8214,7 +8214,7 @@
         <v>PASS</v>
       </c>
       <c r="H266">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I266" t="str">
         <v>Low</v>
@@ -8243,7 +8243,7 @@
         <v>PASS</v>
       </c>
       <c r="H267">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I267" t="str">
         <v>High</v>
@@ -8272,7 +8272,7 @@
         <v>PASS</v>
       </c>
       <c r="H268">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I268" t="str">
         <v>Low</v>
@@ -8301,7 +8301,7 @@
         <v>PASS</v>
       </c>
       <c r="H269">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I269" t="str">
         <v>Critical</v>
@@ -8330,7 +8330,7 @@
         <v>PASS</v>
       </c>
       <c r="H270">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I270" t="str">
         <v>High</v>
@@ -8359,7 +8359,7 @@
         <v>PASS</v>
       </c>
       <c r="H271">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I271" t="str">
         <v>Medium</v>
@@ -8388,7 +8388,7 @@
         <v>PASS</v>
       </c>
       <c r="H272">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I272" t="str">
         <v>Low</v>
@@ -8417,7 +8417,7 @@
         <v>PASS</v>
       </c>
       <c r="H273">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I273" t="str">
         <v>Medium</v>
@@ -8446,7 +8446,7 @@
         <v>PASS</v>
       </c>
       <c r="H274">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I274" t="str">
         <v>High</v>
@@ -8475,7 +8475,7 @@
         <v>PASS</v>
       </c>
       <c r="H275">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I275" t="str">
         <v>Critical</v>
@@ -8504,7 +8504,7 @@
         <v>PASS</v>
       </c>
       <c r="H276">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I276" t="str">
         <v>Low</v>
@@ -8533,7 +8533,7 @@
         <v>PASS</v>
       </c>
       <c r="H277">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I277" t="str">
         <v>High</v>
@@ -8562,7 +8562,7 @@
         <v>PASS</v>
       </c>
       <c r="H278">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I278" t="str">
         <v>Low</v>
@@ -8591,7 +8591,7 @@
         <v>PASS</v>
       </c>
       <c r="H279">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I279" t="str">
         <v>Critical</v>
@@ -8620,7 +8620,7 @@
         <v>PASS</v>
       </c>
       <c r="H280">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I280" t="str">
         <v>High</v>
@@ -8649,7 +8649,7 @@
         <v>PASS</v>
       </c>
       <c r="H281">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I281" t="str">
         <v>Medium</v>
@@ -8678,7 +8678,7 @@
         <v>PASS</v>
       </c>
       <c r="H282">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I282" t="str">
         <v>Low</v>
@@ -8707,7 +8707,7 @@
         <v>PASS</v>
       </c>
       <c r="H283">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I283" t="str">
         <v>Medium</v>
@@ -8736,7 +8736,7 @@
         <v>PASS</v>
       </c>
       <c r="H284">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I284" t="str">
         <v>High</v>
@@ -8765,7 +8765,7 @@
         <v>PASS</v>
       </c>
       <c r="H285">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I285" t="str">
         <v>Critical</v>
@@ -8794,7 +8794,7 @@
         <v>PASS</v>
       </c>
       <c r="H286">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I286" t="str">
         <v>Low</v>
@@ -8823,7 +8823,7 @@
         <v>PASS</v>
       </c>
       <c r="H287">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I287" t="str">
         <v>High</v>
@@ -8852,7 +8852,7 @@
         <v>PASS</v>
       </c>
       <c r="H288">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I288" t="str">
         <v>Low</v>
@@ -8881,7 +8881,7 @@
         <v>PASS</v>
       </c>
       <c r="H289">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I289" t="str">
         <v>Critical</v>
@@ -8910,7 +8910,7 @@
         <v>PASS</v>
       </c>
       <c r="H290">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I290" t="str">
         <v>High</v>
@@ -8939,7 +8939,7 @@
         <v>PASS</v>
       </c>
       <c r="H291">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I291" t="str">
         <v>Medium</v>
@@ -8968,7 +8968,7 @@
         <v>PASS</v>
       </c>
       <c r="H292">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I292" t="str">
         <v>Low</v>
@@ -8997,7 +8997,7 @@
         <v>PASS</v>
       </c>
       <c r="H293">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I293" t="str">
         <v>Medium</v>
@@ -9026,7 +9026,7 @@
         <v>PASS</v>
       </c>
       <c r="H294">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I294" t="str">
         <v>High</v>
@@ -9055,7 +9055,7 @@
         <v>PASS</v>
       </c>
       <c r="H295">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I295" t="str">
         <v>Critical</v>
@@ -9084,7 +9084,7 @@
         <v>PASS</v>
       </c>
       <c r="H296">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I296" t="str">
         <v>Low</v>
@@ -9113,7 +9113,7 @@
         <v>PASS</v>
       </c>
       <c r="H297">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I297" t="str">
         <v>High</v>
@@ -9142,7 +9142,7 @@
         <v>PASS</v>
       </c>
       <c r="H298">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I298" t="str">
         <v>Low</v>
@@ -9171,7 +9171,7 @@
         <v>PASS</v>
       </c>
       <c r="H299">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I299" t="str">
         <v>Critical</v>
@@ -9200,7 +9200,7 @@
         <v>PASS</v>
       </c>
       <c r="H300">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I300" t="str">
         <v>High</v>
@@ -9229,7 +9229,7 @@
         <v>PASS</v>
       </c>
       <c r="H301">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I301" t="str">
         <v>Medium</v>
@@ -9258,7 +9258,7 @@
         <v>PASS</v>
       </c>
       <c r="H302">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I302" t="str">
         <v>Low</v>
@@ -9287,7 +9287,7 @@
         <v>PASS</v>
       </c>
       <c r="H303">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I303" t="str">
         <v>Medium</v>
@@ -9316,7 +9316,7 @@
         <v>PASS</v>
       </c>
       <c r="H304">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I304" t="str">
         <v>High</v>
@@ -9345,7 +9345,7 @@
         <v>PASS</v>
       </c>
       <c r="H305">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I305" t="str">
         <v>Critical</v>
@@ -9374,7 +9374,7 @@
         <v>PASS</v>
       </c>
       <c r="H306">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I306" t="str">
         <v>Low</v>
@@ -9403,7 +9403,7 @@
         <v>PASS</v>
       </c>
       <c r="H307">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I307" t="str">
         <v>High</v>
@@ -9432,7 +9432,7 @@
         <v>PASS</v>
       </c>
       <c r="H308">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I308" t="str">
         <v>Low</v>
@@ -9461,7 +9461,7 @@
         <v>PASS</v>
       </c>
       <c r="H309">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I309" t="str">
         <v>Critical</v>
@@ -9490,7 +9490,7 @@
         <v>PASS</v>
       </c>
       <c r="H310">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I310" t="str">
         <v>High</v>
@@ -9519,7 +9519,7 @@
         <v>PASS</v>
       </c>
       <c r="H311">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I311" t="str">
         <v>Medium</v>
@@ -9548,7 +9548,7 @@
         <v>PASS</v>
       </c>
       <c r="H312">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I312" t="str">
         <v>Low</v>
@@ -9577,7 +9577,7 @@
         <v>PASS</v>
       </c>
       <c r="H313">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I313" t="str">
         <v>Medium</v>
@@ -9606,7 +9606,7 @@
         <v>PASS</v>
       </c>
       <c r="H314">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I314" t="str">
         <v>High</v>
@@ -9635,7 +9635,7 @@
         <v>PASS</v>
       </c>
       <c r="H315">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I315" t="str">
         <v>Critical</v>
@@ -9664,7 +9664,7 @@
         <v>PASS</v>
       </c>
       <c r="H316">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I316" t="str">
         <v>Low</v>
@@ -9693,7 +9693,7 @@
         <v>PASS</v>
       </c>
       <c r="H317">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I317" t="str">
         <v>High</v>
@@ -9722,7 +9722,7 @@
         <v>PASS</v>
       </c>
       <c r="H318">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I318" t="str">
         <v>Low</v>
@@ -9751,7 +9751,7 @@
         <v>PASS</v>
       </c>
       <c r="H319">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I319" t="str">
         <v>Critical</v>
@@ -9780,7 +9780,7 @@
         <v>PASS</v>
       </c>
       <c r="H320">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I320" t="str">
         <v>High</v>
@@ -9809,7 +9809,7 @@
         <v>PASS</v>
       </c>
       <c r="H321">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I321" t="str">
         <v>Medium</v>
@@ -9838,7 +9838,7 @@
         <v>PASS</v>
       </c>
       <c r="H322">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I322" t="str">
         <v>Low</v>
@@ -9867,7 +9867,7 @@
         <v>PASS</v>
       </c>
       <c r="H323">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I323" t="str">
         <v>Medium</v>
@@ -9896,7 +9896,7 @@
         <v>PASS</v>
       </c>
       <c r="H324">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I324" t="str">
         <v>High</v>
@@ -9925,7 +9925,7 @@
         <v>PASS</v>
       </c>
       <c r="H325">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I325" t="str">
         <v>Critical</v>
@@ -9954,7 +9954,7 @@
         <v>PASS</v>
       </c>
       <c r="H326">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I326" t="str">
         <v>Low</v>
@@ -10012,7 +10012,7 @@
         <v>PASS</v>
       </c>
       <c r="H328">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I328" t="str">
         <v>Low</v>
@@ -10041,7 +10041,7 @@
         <v>PASS</v>
       </c>
       <c r="H329">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I329" t="str">
         <v>Critical</v>
@@ -10070,7 +10070,7 @@
         <v>PASS</v>
       </c>
       <c r="H330">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I330" t="str">
         <v>High</v>
@@ -10099,7 +10099,7 @@
         <v>PASS</v>
       </c>
       <c r="H331">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I331" t="str">
         <v>Medium</v>
@@ -10128,7 +10128,7 @@
         <v>PASS</v>
       </c>
       <c r="H332">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I332" t="str">
         <v>Low</v>
@@ -10157,7 +10157,7 @@
         <v>PASS</v>
       </c>
       <c r="H333">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I333" t="str">
         <v>Medium</v>
@@ -10186,7 +10186,7 @@
         <v>PASS</v>
       </c>
       <c r="H334">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I334" t="str">
         <v>High</v>
@@ -10215,7 +10215,7 @@
         <v>PASS</v>
       </c>
       <c r="H335">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I335" t="str">
         <v>Critical</v>
@@ -10244,7 +10244,7 @@
         <v>PASS</v>
       </c>
       <c r="H336">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I336" t="str">
         <v>Low</v>
@@ -10273,7 +10273,7 @@
         <v>PASS</v>
       </c>
       <c r="H337">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I337" t="str">
         <v>High</v>
@@ -10302,7 +10302,7 @@
         <v>PASS</v>
       </c>
       <c r="H338">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I338" t="str">
         <v>Low</v>
@@ -10331,7 +10331,7 @@
         <v>PASS</v>
       </c>
       <c r="H339">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I339" t="str">
         <v>Critical</v>
@@ -10360,7 +10360,7 @@
         <v>PASS</v>
       </c>
       <c r="H340">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I340" t="str">
         <v>High</v>
@@ -10389,7 +10389,7 @@
         <v>PASS</v>
       </c>
       <c r="H341">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I341" t="str">
         <v>Medium</v>
@@ -10418,7 +10418,7 @@
         <v>PASS</v>
       </c>
       <c r="H342">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I342" t="str">
         <v>Low</v>
@@ -10447,7 +10447,7 @@
         <v>PASS</v>
       </c>
       <c r="H343">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I343" t="str">
         <v>Medium</v>
@@ -10476,7 +10476,7 @@
         <v>PASS</v>
       </c>
       <c r="H344">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I344" t="str">
         <v>High</v>
@@ -10505,7 +10505,7 @@
         <v>PASS</v>
       </c>
       <c r="H345">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I345" t="str">
         <v>Critical</v>
@@ -10534,7 +10534,7 @@
         <v>PASS</v>
       </c>
       <c r="H346">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I346" t="str">
         <v>Low</v>
@@ -10563,7 +10563,7 @@
         <v>PASS</v>
       </c>
       <c r="H347">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I347" t="str">
         <v>High</v>
@@ -10592,7 +10592,7 @@
         <v>PASS</v>
       </c>
       <c r="H348">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I348" t="str">
         <v>Low</v>
@@ -10621,7 +10621,7 @@
         <v>PASS</v>
       </c>
       <c r="H349">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I349" t="str">
         <v>Critical</v>
@@ -10650,7 +10650,7 @@
         <v>PASS</v>
       </c>
       <c r="H350">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I350" t="str">
         <v>High</v>
@@ -10679,7 +10679,7 @@
         <v>PASS</v>
       </c>
       <c r="H351">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I351" t="str">
         <v>Medium</v>
